--- a/students.xlsx
+++ b/students.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\website\CYBER NOVA INSTITUTE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HTML learning\Projects\Smart Digital Certificate &amp; Bulk Credential Engine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4F540A-0113-47A6-B01D-1E7AFF80AB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74FF973C-D1E3-4C27-9FE0-F37868F3B8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="First Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>certificate_id</t>
   </si>
@@ -42,29 +37,86 @@
     <t>issue_date</t>
   </si>
   <si>
+    <t>CNCA-2026-7</t>
+  </si>
+  <si>
+    <t>Abdul Ahad</t>
+  </si>
+  <si>
+    <t>Graphic Designing</t>
+  </si>
+  <si>
+    <t>d60163abcf4936754e482716579564c4cd34740070b68c77ddd10f4eb5c82698</t>
+  </si>
+  <si>
     <t>CNCA-2026-1</t>
   </si>
   <si>
-    <t>Hassan</t>
-  </si>
-  <si>
-    <t>Python programing</t>
-  </si>
-  <si>
-    <t>#54648298</t>
+    <t>Abdul Wasay</t>
+  </si>
+  <si>
+    <t>Python Programming</t>
+  </si>
+  <si>
+    <t>b01c14e571b60df889e4bcfb2312444793d9678d7c42381ff302f3ecea6e07ef</t>
+  </si>
+  <si>
+    <t>CNCA-2026-2</t>
+  </si>
+  <si>
+    <t>Abdul Basit</t>
+  </si>
+  <si>
+    <t>9ad36ca53e6f36eac11658e804344aa6fc9f4dd6890274536c0fcad18bdeac49</t>
+  </si>
+  <si>
+    <t>CNCA-2026-3</t>
+  </si>
+  <si>
+    <t>Abdul Hadi</t>
+  </si>
+  <si>
+    <t>Basic Computer &amp; MS Office</t>
+  </si>
+  <si>
+    <t>552aea286dd4e4442784dfe08994b78aa55e8aeb8dc305648ff590f8d007afb5</t>
+  </si>
+  <si>
+    <t>CNCA-2026-4</t>
+  </si>
+  <si>
+    <t>Muhammad Abdullah</t>
+  </si>
+  <si>
+    <t>b7e739e773e124df844ddde8e62380c2424e59893afcd03e79d2f613863735be</t>
+  </si>
+  <si>
+    <t>CNCA-2026-5</t>
+  </si>
+  <si>
+    <t>Ali Zia</t>
+  </si>
+  <si>
+    <t>7a321d4a133e448673209b9faf987105c6f92108408a9ed7c783c8f73dcf1504</t>
+  </si>
+  <si>
+    <t>CNCA-2026-6</t>
+  </si>
+  <si>
+    <t>Abdul Rafay</t>
+  </si>
+  <si>
+    <t>541a89eebb63f91c17899a3dca0afb8ad53ce24e75be73531c531160d98c87a1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -90,11 +142,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -129,7 +179,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -141,7 +191,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -188,6 +238,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -223,6 +290,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -375,14 +459,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="68.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -412,324 +496,114 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2">
-        <v>46358</v>
+      <c r="E2" s="1">
+        <v>46153</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E3" s="3"/>
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1">
+        <v>46236</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E4" s="3"/>
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1">
+        <v>46237</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E5" s="3"/>
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1">
+        <v>46238</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E6" s="3"/>
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1">
+        <v>46239</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E7" s="3"/>
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1">
+        <v>46240</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E14" s="3"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E26" s="3"/>
-    </row>
-    <row r="27" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E27" s="3"/>
-    </row>
-    <row r="28" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E28" s="3"/>
-    </row>
-    <row r="29" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E29" s="3"/>
-    </row>
-    <row r="30" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E30" s="3"/>
-    </row>
-    <row r="31" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E31" s="3"/>
-    </row>
-    <row r="32" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E32" s="3"/>
-    </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E33" s="3"/>
-    </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E34" s="3"/>
-    </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E35" s="3"/>
-    </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E36" s="3"/>
-    </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E37" s="3"/>
-    </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E38" s="3"/>
-    </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E39" s="3"/>
-    </row>
-    <row r="40" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E40" s="3"/>
-    </row>
-    <row r="41" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E41" s="3"/>
-    </row>
-    <row r="42" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E42" s="3"/>
-    </row>
-    <row r="43" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E43" s="3"/>
-    </row>
-    <row r="44" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E45" s="3"/>
-    </row>
-    <row r="46" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E46" s="3"/>
-    </row>
-    <row r="47" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E47" s="3"/>
-    </row>
-    <row r="48" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E50" s="3"/>
-    </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E51" s="3"/>
-    </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E52" s="3"/>
-    </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E53" s="3"/>
-    </row>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E54" s="3"/>
-    </row>
-    <row r="55" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E55" s="3"/>
-    </row>
-    <row r="56" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E56" s="3"/>
-    </row>
-    <row r="57" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E57" s="3"/>
-    </row>
-    <row r="58" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E58" s="3"/>
-    </row>
-    <row r="59" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E59" s="3"/>
-    </row>
-    <row r="60" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E60" s="3"/>
-    </row>
-    <row r="61" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E61" s="3"/>
-    </row>
-    <row r="62" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E62" s="3"/>
-    </row>
-    <row r="63" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E63" s="3"/>
-    </row>
-    <row r="64" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E64" s="3"/>
-    </row>
-    <row r="65" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E65" s="3"/>
-    </row>
-    <row r="66" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E66" s="3"/>
-    </row>
-    <row r="67" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E67" s="3"/>
-    </row>
-    <row r="68" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E68" s="3"/>
-    </row>
-    <row r="69" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E69" s="3"/>
-    </row>
-    <row r="70" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E70" s="3"/>
-    </row>
-    <row r="71" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E71" s="3"/>
-    </row>
-    <row r="72" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E72" s="3"/>
-    </row>
-    <row r="73" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E73" s="3"/>
-    </row>
-    <row r="74" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E74" s="3"/>
-    </row>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E75" s="3"/>
-    </row>
-    <row r="76" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E76" s="3"/>
-    </row>
-    <row r="77" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E77" s="3"/>
-    </row>
-    <row r="78" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E78" s="3"/>
-    </row>
-    <row r="79" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E79" s="3"/>
-    </row>
-    <row r="80" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E80" s="3"/>
-    </row>
-    <row r="81" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E81" s="3"/>
-    </row>
-    <row r="82" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E82" s="3"/>
-    </row>
-    <row r="83" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E83" s="3"/>
-    </row>
-    <row r="84" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E84" s="3"/>
-    </row>
-    <row r="85" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E85" s="3"/>
-    </row>
-    <row r="86" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E86" s="3"/>
-    </row>
-    <row r="87" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E87" s="3"/>
-    </row>
-    <row r="88" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E88" s="3"/>
-    </row>
-    <row r="89" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E89" s="3"/>
-    </row>
-    <row r="90" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E90" s="3"/>
-    </row>
-    <row r="91" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E91" s="3"/>
-    </row>
-    <row r="92" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E92" s="3"/>
-    </row>
-    <row r="93" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E93" s="3"/>
-    </row>
-    <row r="94" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E94" s="3"/>
-    </row>
-    <row r="95" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E95" s="3"/>
-    </row>
-    <row r="96" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E96" s="3"/>
-    </row>
-    <row r="97" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E97" s="3"/>
-    </row>
-    <row r="98" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E98" s="3"/>
-    </row>
-    <row r="99" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E99" s="3"/>
-    </row>
-    <row r="100" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E100" s="3"/>
-    </row>
-    <row r="101" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E101" s="3"/>
-    </row>
-    <row r="102" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E102" s="3"/>
-    </row>
-    <row r="103" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E103" s="3"/>
-    </row>
-    <row r="104" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E104" s="3"/>
-    </row>
-    <row r="105" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E105" s="3"/>
-    </row>
-    <row r="106" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E106" s="3"/>
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="1">
+        <v>46241</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
